--- a/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346CE935-3869-41A5-9B2E-7CAD390712B7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CCDADE-E7AC-42E2-BB3F-472C4DFF761B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>

--- a/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CCDADE-E7AC-42E2-BB3F-472C4DFF761B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558776CB-3161-4D13-AB82-6F1A5B799608}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | MAY" sheetId="902" r:id="rId1"/>
@@ -37156,7 +37156,7 @@
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
       <c r="F36" s="42">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="G36" s="42">
         <v>1</v>
@@ -37330,7 +37330,7 @@
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
       <c r="F42" s="42">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="G42" s="42">
         <v>1</v>

--- a/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558776CB-3161-4D13-AB82-6F1A5B799608}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A374295B-3C75-4F5B-B3B3-F5BAC80FDECD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | MAY" sheetId="902" r:id="rId1"/>
@@ -46110,12 +46110,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="F8" s="14">
+        <v>5</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>32</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -46130,9 +46136,15 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>15</v>
+      </c>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -46298,12 +46310,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>10</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -46318,20 +46336,32 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>2</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="F16" s="27">
+        <v>5</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>22</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -46346,9 +46376,15 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>15</v>
+      </c>
+      <c r="X16" s="62">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -46750,17 +46786,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>54</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>14</v>
+      </c>
+      <c r="M24" s="14">
+        <v>790</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -46936,17 +46984,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>47</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>12</v>
+      </c>
+      <c r="M31" s="23">
+        <v>4</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -46964,17 +47024,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>7</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>2</v>
+      </c>
+      <c r="M32" s="28">
+        <v>786</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -47111,20 +47183,42 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>6</v>
+      </c>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="E36" s="42">
+        <v>21</v>
+      </c>
+      <c r="F36" s="42">
+        <v>677</v>
+      </c>
+      <c r="G36" s="42">
+        <v>23</v>
+      </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
+      <c r="I36" s="42">
+        <v>28</v>
+      </c>
+      <c r="J36" s="42">
+        <v>2</v>
+      </c>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
+      <c r="L36" s="42">
+        <v>15</v>
+      </c>
+      <c r="M36" s="42">
+        <v>11</v>
+      </c>
+      <c r="N36" s="42">
+        <v>21</v>
+      </c>
+      <c r="O36" s="42">
+        <v>7</v>
+      </c>
+      <c r="P36" s="42">
+        <v>14</v>
+      </c>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
@@ -47269,20 +47363,42 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>6</v>
+      </c>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="E42" s="42">
+        <v>21</v>
+      </c>
+      <c r="F42" s="42">
+        <v>677</v>
+      </c>
+      <c r="G42" s="42">
+        <v>23</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+      <c r="I42" s="42">
+        <v>28</v>
+      </c>
+      <c r="J42" s="42">
+        <v>2</v>
+      </c>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
+      <c r="L42" s="42">
+        <v>15</v>
+      </c>
+      <c r="M42" s="42">
+        <v>11</v>
+      </c>
+      <c r="N42" s="42">
+        <v>21</v>
+      </c>
+      <c r="O42" s="42">
+        <v>7</v>
+      </c>
+      <c r="P42" s="42">
+        <v>14</v>
+      </c>
       <c r="Q42" s="43"/>
       <c r="R42" s="83" t="s">
         <v>54</v>
@@ -47325,7 +47441,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
+      <c r="C44" s="91">
+        <f>2+5+22+15+2+2+7+2+786</f>
+        <v>843</v>
+      </c>
       <c r="D44" s="91"/>
       <c r="E44" s="91"/>
     </row>

--- a/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A374295B-3C75-4F5B-B3B3-F5BAC80FDECD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454B516E-961A-4C49-A65F-1177A810D98B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | MAY" sheetId="902" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="95">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -357,6 +357,30 @@
   </si>
   <si>
     <t>DATE ___________05/02/2026___________</t>
+  </si>
+  <si>
+    <t>3/23b</t>
+  </si>
+  <si>
+    <t>9/15b</t>
+  </si>
+  <si>
+    <t>13/14b</t>
+  </si>
+  <si>
+    <t>3/12b</t>
+  </si>
+  <si>
+    <t>12/22b</t>
+  </si>
+  <si>
+    <t>13/22b</t>
+  </si>
+  <si>
+    <t>2/4b</t>
+  </si>
+  <si>
+    <t>16/12b</t>
   </si>
 </sst>
 </file>
@@ -1815,7 +1839,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -2184,12 +2209,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -2205,8 +2238,12 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -2372,12 +2409,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="F15" s="23">
+        <v>1</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>1</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -2393,19 +2438,31 @@
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="F16" s="27">
+        <v>0</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>91</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -2421,8 +2478,12 @@
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -2824,17 +2885,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>30</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>6</v>
+      </c>
+      <c r="M24" s="14">
+        <v>382</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -3010,17 +3083,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>9</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>1</v>
+      </c>
+      <c r="M31" s="23">
+        <v>38</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>93</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -3038,17 +3123,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>21</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>5</v>
+      </c>
+      <c r="M32" s="28">
+        <v>344</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -3188,18 +3285,32 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>369</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>4</v>
+      </c>
+      <c r="I36" s="42">
+        <v>5</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>7</v>
+      </c>
+      <c r="P36" s="42">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>3</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -3346,18 +3457,32 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>369</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>4</v>
+      </c>
+      <c r="I42" s="42">
+        <v>5</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>7</v>
+      </c>
+      <c r="P42" s="42">
+        <v>11</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>3</v>
+      </c>
       <c r="R42" s="83" t="s">
         <v>54</v>
       </c>
@@ -3399,7 +3524,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
+      <c r="C44" s="91">
+        <f>12+21+5+344</f>
+        <v>382</v>
+      </c>
       <c r="D44" s="91"/>
       <c r="E44" s="91"/>
     </row>
@@ -3407,7 +3535,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
+      <c r="C45" s="91">
+        <f>22</f>
+        <v>22</v>
+      </c>
       <c r="D45" s="91"/>
       <c r="E45" s="91"/>
     </row>
@@ -3437,7 +3568,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -3806,12 +3938,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>20</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -3827,8 +3963,12 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -3994,12 +4134,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>2</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>90</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -4015,19 +4159,27 @@
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="X15" s="61">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>94</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -4043,8 +4195,12 @@
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -4446,17 +4602,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>20</v>
+      </c>
+      <c r="M24" s="14">
+        <v>544</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -4632,17 +4800,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>2</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>9</v>
+      </c>
+      <c r="M31" s="23">
+        <v>60</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -4660,17 +4840,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>58</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>11</v>
+      </c>
+      <c r="M32" s="28">
+        <v>484</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -4810,18 +5002,38 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="F36" s="42">
+        <v>529</v>
+      </c>
+      <c r="G36" s="42">
+        <v>22</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>10</v>
+      </c>
+      <c r="J36" s="42">
+        <v>3</v>
+      </c>
+      <c r="K36" s="42">
+        <v>8</v>
+      </c>
+      <c r="L36" s="42">
+        <v>2</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>13</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>13</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -4968,18 +5180,38 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="F42" s="42">
+        <v>529</v>
+      </c>
+      <c r="G42" s="42">
+        <v>22</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>10</v>
+      </c>
+      <c r="J42" s="42">
+        <v>3</v>
+      </c>
+      <c r="K42" s="42">
+        <v>8</v>
+      </c>
+      <c r="L42" s="42">
+        <v>2</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>13</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>13</v>
+      </c>
       <c r="R42" s="83" t="s">
         <v>54</v>
       </c>
@@ -5021,7 +5253,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
+      <c r="C44" s="91">
+        <f>16+2+58+11+484</f>
+        <v>571</v>
+      </c>
       <c r="D44" s="91"/>
       <c r="E44" s="91"/>
     </row>
@@ -5029,7 +5264,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
+      <c r="C45" s="91">
+        <v>12</v>
+      </c>
       <c r="D45" s="91"/>
       <c r="E45" s="91"/>
     </row>
@@ -49084,7 +49321,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -49453,12 +49691,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -49473,9 +49715,15 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -49641,12 +49889,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>88</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -49661,20 +49913,30 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>87</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -49689,9 +49951,15 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>2</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -50093,17 +50361,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>26</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>11</v>
+      </c>
+      <c r="M24" s="14">
+        <v>370</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>3</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -50279,17 +50559,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>2</v>
+      </c>
+      <c r="M31" s="23">
+        <v>26</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>3</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -50307,17 +50599,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>25</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>9</v>
+      </c>
+      <c r="M32" s="28">
+        <v>344</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -50456,19 +50760,45 @@
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="E36" s="42">
+        <v>1</v>
+      </c>
+      <c r="F36" s="42">
+        <v>358</v>
+      </c>
+      <c r="G36" s="42">
+        <v>3</v>
+      </c>
+      <c r="H36" s="42">
+        <v>7</v>
+      </c>
+      <c r="I36" s="42">
+        <v>7</v>
+      </c>
+      <c r="J36" s="42">
+        <v>8</v>
+      </c>
+      <c r="K36" s="42">
+        <v>9</v>
+      </c>
+      <c r="L36" s="42">
+        <v>1</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>8</v>
+      </c>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>22</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -50614,19 +50944,45 @@
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="E42" s="42">
+        <v>1</v>
+      </c>
+      <c r="F42" s="42">
+        <v>358</v>
+      </c>
+      <c r="G42" s="42">
+        <v>3</v>
+      </c>
+      <c r="H42" s="42">
+        <v>7</v>
+      </c>
+      <c r="I42" s="42">
+        <v>7</v>
+      </c>
+      <c r="J42" s="42">
+        <v>8</v>
+      </c>
+      <c r="K42" s="42">
+        <v>9</v>
+      </c>
+      <c r="L42" s="42">
+        <v>1</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>8</v>
+      </c>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>22</v>
+      </c>
       <c r="R42" s="83" t="s">
         <v>54</v>
       </c>
@@ -50668,7 +51024,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
+      <c r="C44" s="91">
+        <f>3+2+25+9+344</f>
+        <v>383</v>
+      </c>
       <c r="D44" s="91"/>
       <c r="E44" s="91"/>
     </row>
@@ -50676,7 +51035,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
+      <c r="C45" s="91">
+        <v>23</v>
+      </c>
       <c r="D45" s="91"/>
       <c r="E45" s="91"/>
     </row>

--- a/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454B516E-961A-4C49-A65F-1177A810D98B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F68805-AC11-4A9E-8EB7-0F8F1DFEC4EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | MAY" sheetId="902" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F68805-AC11-4A9E-8EB7-0F8F1DFEC4EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A473CFA-A0C8-4A3A-A4A3-9D5EDCFBC30C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="14" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | MAY" sheetId="902" r:id="rId1"/>
@@ -64,9 +64,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="8">'05-04 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'05-04 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'05-04 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'05-05 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'05-05 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'05-05 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'05-05 R1'!$A$1:$Z$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'05-05 R2'!$A$1:$Z$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'05-05 R3'!$A$1:$Z$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'05-06 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'05-06 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'05-06 R3'!$A$1:$V$44</definedName>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="102">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -381,6 +381,27 @@
   </si>
   <si>
     <t>16/12b</t>
+  </si>
+  <si>
+    <t>23/12B</t>
+  </si>
+  <si>
+    <t>21/12B</t>
+  </si>
+  <si>
+    <t>5/6B</t>
+  </si>
+  <si>
+    <t>14/9B</t>
+  </si>
+  <si>
+    <t>19/15B</t>
+  </si>
+  <si>
+    <t>3/2B</t>
+  </si>
+  <si>
+    <t>5/4B</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1022,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1283,6 +1304,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -6898,7 +6923,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -7267,12 +7293,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>99</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -7287,9 +7321,15 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>6</v>
+      </c>
+      <c r="X8" s="59">
+        <v>7</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -7455,12 +7495,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>98</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -7475,20 +7523,34 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>1</v>
+      </c>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>97</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -7503,9 +7565,15 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>6</v>
+      </c>
+      <c r="X16" s="62">
+        <v>5</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -7907,23 +7975,39 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>7</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>109</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>12</v>
+      </c>
+      <c r="M24" s="14">
+        <v>566</v>
+      </c>
+      <c r="N24" s="14">
+        <v>1</v>
+      </c>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>8</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -8093,23 +8177,39 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>108</v>
+      </c>
+      <c r="N31" s="23">
+        <v>0</v>
+      </c>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>0</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="23">
+        <v>0</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="61"/>
       <c r="Y31" s="24"/>
@@ -8121,23 +8221,39 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>7</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>128</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>12</v>
+      </c>
+      <c r="M32" s="28">
+        <v>458</v>
+      </c>
+      <c r="N32" s="28">
+        <v>1</v>
+      </c>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>8</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="V32" s="28">
+        <v>1</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="63"/>
       <c r="Y32" s="29"/>
@@ -8268,21 +8384,49 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="C36" s="46">
+        <v>4</v>
+      </c>
+      <c r="D36" s="41">
+        <v>2</v>
+      </c>
+      <c r="E36" s="42">
+        <v>22</v>
+      </c>
+      <c r="F36" s="42">
+        <v>585</v>
+      </c>
+      <c r="G36" s="42">
+        <v>12</v>
+      </c>
+      <c r="H36" s="42">
+        <v>7</v>
+      </c>
+      <c r="I36" s="42">
+        <v>14</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>11</v>
+      </c>
+      <c r="L36" s="42">
+        <v>8</v>
+      </c>
+      <c r="M36" s="42">
+        <v>5</v>
+      </c>
+      <c r="N36" s="42">
+        <v>17</v>
+      </c>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>6</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -8426,21 +8570,49 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="C42" s="46">
+        <v>4</v>
+      </c>
+      <c r="D42" s="41">
+        <v>2</v>
+      </c>
+      <c r="E42" s="42">
+        <v>22</v>
+      </c>
+      <c r="F42" s="42">
+        <v>585</v>
+      </c>
+      <c r="G42" s="42">
+        <v>12</v>
+      </c>
+      <c r="H42" s="42">
+        <v>7</v>
+      </c>
+      <c r="I42" s="42">
+        <v>14</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>11</v>
+      </c>
+      <c r="L42" s="42">
+        <v>8</v>
+      </c>
+      <c r="M42" s="42">
+        <v>5</v>
+      </c>
+      <c r="N42" s="42">
+        <v>17</v>
+      </c>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>6</v>
+      </c>
       <c r="R42" s="83" t="s">
         <v>54</v>
       </c>
@@ -8482,7 +8654,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
+      <c r="C44" s="91">
+        <f>1+2+1+5+6+5+2+7+128+12+458+1+8+1</f>
+        <v>637</v>
+      </c>
       <c r="D44" s="91"/>
       <c r="E44" s="91"/>
     </row>
@@ -8490,7 +8665,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
+      <c r="C45" s="91">
+        <v>6</v>
+      </c>
       <c r="D45" s="91"/>
       <c r="E45" s="91"/>
     </row>
@@ -8889,12 +9066,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>12</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -8910,8 +9095,12 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -9077,12 +9266,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -9098,19 +9295,31 @@
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>12</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -9126,8 +9335,12 @@
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -9529,17 +9742,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>72</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>11</v>
+      </c>
+      <c r="M24" s="14">
+        <v>524</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>101</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -9715,17 +9940,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>13</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>110</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>101</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -9743,17 +9980,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>59</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>11</v>
+      </c>
+      <c r="M32" s="28">
+        <v>414</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -9890,21 +10139,39 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>487</v>
+      </c>
+      <c r="G36" s="42">
+        <v>14</v>
+      </c>
+      <c r="H36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="42">
+        <v>16</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="K36" s="42">
+        <v>4</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>7</v>
+      </c>
+      <c r="P36" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>11</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -10048,21 +10315,39 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>487</v>
+      </c>
+      <c r="G42" s="42">
+        <v>14</v>
+      </c>
+      <c r="H42" s="42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="42">
+        <v>16</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="K42" s="42">
+        <v>4</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>7</v>
+      </c>
+      <c r="P42" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>11</v>
+      </c>
       <c r="R42" s="83" t="s">
         <v>54</v>
       </c>
@@ -10104,7 +10389,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
+      <c r="C44" s="91">
+        <f>1+12+59+11+414</f>
+        <v>497</v>
+      </c>
       <c r="D44" s="91"/>
       <c r="E44" s="91"/>
     </row>
@@ -10131,7 +10419,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10142,7 +10430,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -10511,12 +10800,22 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="C8" s="13">
+        <v>5</v>
+      </c>
+      <c r="D8" s="14">
+        <v>5</v>
+      </c>
+      <c r="E8" s="14">
+        <v>22</v>
+      </c>
+      <c r="F8" s="14">
+        <v>23</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="92" t="s">
+        <v>95</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -10532,8 +10831,12 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -10699,12 +11002,22 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>2</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -10720,19 +11033,33 @@
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="X15" s="61">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="C16" s="57">
+        <v>5</v>
+      </c>
+      <c r="D16" s="58">
+        <v>5</v>
+      </c>
+      <c r="E16" s="27">
+        <v>22</v>
+      </c>
+      <c r="F16" s="27">
+        <v>23</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>96</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -10748,8 +11075,12 @@
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -11151,17 +11482,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>74</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>20</v>
+      </c>
+      <c r="M24" s="14">
+        <v>545</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -11337,17 +11680,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>2</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>8</v>
+      </c>
+      <c r="M31" s="23">
+        <v>3</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -11365,17 +11720,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>72</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>12</v>
+      </c>
+      <c r="M32" s="28">
+        <v>542</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -11670,19 +12037,29 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>688</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
       <c r="I42" s="42"/>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
       <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>13</v>
+      </c>
+      <c r="O42" s="42">
+        <v>11</v>
+      </c>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
       <c r="R42" s="83" t="s">
@@ -11726,7 +12103,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
+      <c r="C44" s="91">
+        <f>5+5+22+23+21+2+72+12+542</f>
+        <v>704</v>
+      </c>
       <c r="D44" s="91"/>
       <c r="E44" s="91"/>
     </row>
@@ -11734,7 +12114,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
+      <c r="C45" s="91">
+        <f>12</f>
+        <v>12</v>
+      </c>
       <c r="D45" s="91"/>
       <c r="E45" s="91"/>
     </row>
@@ -11753,7 +12136,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A473CFA-A0C8-4A3A-A4A3-9D5EDCFBC30C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE97337C-16F8-4A6C-BEF7-138D71CACE82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="14" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="16" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | MAY" sheetId="902" r:id="rId1"/>
@@ -1269,6 +1269,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1304,10 +1308,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3208,47 +3208,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3508,12 +3508,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -3549,23 +3549,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>12+21+5+344</f>
         <v>382</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <f>22</f>
         <v>22</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4925,47 +4925,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -5237,12 +5237,12 @@
       <c r="Q42" s="43">
         <v>13</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -5278,22 +5278,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>16+2+58+11+484</f>
         <v>571</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <v>12</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6590,47 +6590,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6862,12 +6862,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8285,47 +8285,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -8613,12 +8613,12 @@
       <c r="Q42" s="43">
         <v>6</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8654,22 +8654,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+2+1+5+6+5+2+7+128+12+458+1+8+1</f>
         <v>637</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <v>6</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -10040,47 +10040,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -10348,12 +10348,12 @@
       <c r="Q42" s="43">
         <v>11</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -10389,20 +10389,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+12+59+11+414</f>
         <v>497</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -10813,7 +10813,7 @@
         <v>23</v>
       </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="92" t="s">
+      <c r="H8" s="80" t="s">
         <v>95</v>
       </c>
       <c r="I8" s="14"/>
@@ -11780,47 +11780,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -12062,12 +12062,12 @@
       </c>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -12103,23 +12103,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>5+5+22+23+21+2+72+12+542</f>
         <v>704</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <f>12</f>
         <v>12</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13416,47 +13416,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -13688,12 +13688,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -15020,47 +15020,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -15292,12 +15292,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -15333,17 +15333,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -16642,47 +16642,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16914,12 +16914,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -16955,17 +16955,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -18264,47 +18264,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -18536,12 +18536,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18577,17 +18577,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19884,47 +19884,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -20156,12 +20156,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21486,47 +21486,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21758,12 +21758,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -23090,47 +23090,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -23362,12 +23362,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -23403,17 +23403,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -24712,47 +24712,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -24984,12 +24984,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -25025,17 +25025,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -26334,47 +26334,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -26606,12 +26606,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26647,17 +26647,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -27954,47 +27954,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -28226,12 +28226,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -29558,47 +29558,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -29830,12 +29830,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -29871,17 +29871,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -31180,47 +31180,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -31452,12 +31452,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -31493,17 +31493,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -32802,47 +32802,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -33074,12 +33074,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -33115,17 +33115,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -34422,47 +34422,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -34694,12 +34694,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -36026,47 +36026,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -36298,12 +36298,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -36339,17 +36339,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -37673,47 +37673,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -37977,12 +37977,12 @@
       <c r="Q42" s="43">
         <v>22</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -38018,22 +38018,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>25+3+704</f>
         <v>732</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <v>3</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -39332,47 +39332,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -39604,12 +39604,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -39645,17 +39645,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -40954,47 +40954,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -41226,12 +41226,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -41267,17 +41267,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -42660,47 +42660,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -42964,12 +42964,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -43005,22 +43005,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+7+1+7+6+272+1</f>
         <v>295</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <v>5</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -44385,47 +44385,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -44677,12 +44677,12 @@
         <v>2</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -44718,20 +44718,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+1+19+56+7+530</f>
         <v>614</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -46028,47 +46028,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -46300,12 +46300,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -47704,47 +47704,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -48020,12 +48020,12 @@
         <v>14</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -48061,20 +48061,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>2+5+22+15+2+2+7+2+786</f>
         <v>843</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -49371,47 +49371,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -49643,12 +49643,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -51042,47 +51042,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -51366,12 +51366,12 @@
       <c r="Q42" s="43">
         <v>22</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -51407,22 +51407,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>3+2+25+9+344</f>
         <v>383</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <v>23</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/CSR MONTH OF MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE97337C-16F8-4A6C-BEF7-138D71CACE82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8F1E78-DDAF-4A22-9A43-B25B1CFF25EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="16" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="18" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | MAY" sheetId="902" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2689" uniqueCount="108">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -402,6 +402,24 @@
   </si>
   <si>
     <t>5/4B</t>
+  </si>
+  <si>
+    <t>11/15B</t>
+  </si>
+  <si>
+    <t>10/9B</t>
+  </si>
+  <si>
+    <t>3/18B</t>
+  </si>
+  <si>
+    <t>20B</t>
+  </si>
+  <si>
+    <t>3/20B</t>
+  </si>
+  <si>
+    <t>10/11B</t>
   </si>
 </sst>
 </file>
@@ -13749,10 +13767,13 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" style="2" customWidth="1"/>
     <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -14118,12 +14139,22 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -14139,8 +14170,12 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="X8" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -14306,12 +14341,22 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>102</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -14327,19 +14372,33 @@
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="X15" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="C16" s="57">
+        <v>1</v>
+      </c>
+      <c r="D16" s="58">
+        <v>1</v>
+      </c>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>104</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -14355,8 +14414,12 @@
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="X16" s="62">
+        <v>3</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -14758,14 +14821,24 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>4</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>23</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>67</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="M24" s="14">
+        <v>324</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -14944,14 +15017,24 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>71</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -14972,14 +15055,24 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>4</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>22</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>67</v>
+      </c>
+      <c r="L32" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="M32" s="28">
+        <v>253</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -15121,19 +15214,39 @@
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="E36" s="42">
+        <v>1</v>
+      </c>
+      <c r="F36" s="42">
+        <v>273</v>
+      </c>
+      <c r="G36" s="42">
+        <v>5</v>
+      </c>
+      <c r="H36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="42">
+        <v>3</v>
+      </c>
+      <c r="J36" s="42">
+        <v>3</v>
+      </c>
+      <c r="K36" s="42">
+        <v>6</v>
+      </c>
+      <c r="L36" s="42">
+        <v>77</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>6</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -15279,19 +15392,39 @@
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="E42" s="42">
+        <v>1</v>
+      </c>
+      <c r="F42" s="42">
+        <v>273</v>
+      </c>
+      <c r="G42" s="42">
+        <v>5</v>
+      </c>
+      <c r="H42" s="42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="42">
+        <v>3</v>
+      </c>
+      <c r="J42" s="42">
+        <v>3</v>
+      </c>
+      <c r="K42" s="42">
+        <v>6</v>
+      </c>
+      <c r="L42" s="42">
+        <v>77</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>6</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -15333,7 +15466,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>1+1+1+1+3+31+4+22+67+10+253</f>
+        <v>394</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -15341,7 +15477,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
+      <c r="C45" s="92">
+        <f>18+11</f>
+        <v>29</v>
+      </c>
       <c r="D45" s="92"/>
       <c r="E45" s="92"/>
     </row>
@@ -15740,12 +15879,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>13</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -15761,8 +15906,12 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -15928,12 +16077,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -15949,19 +16104,29 @@
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>13</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -15977,8 +16142,12 @@
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -16380,17 +16549,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>67</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>465</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>101</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -16566,17 +16747,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>13</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>97</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>101</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -16594,17 +16787,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>54</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>10</v>
+      </c>
+      <c r="M32" s="28">
+        <v>368</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -16744,17 +16949,27 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="F36" s="42">
+        <v>430</v>
+      </c>
+      <c r="G36" s="42">
+        <v>4</v>
+      </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>11</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
       <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
+      <c r="P36" s="42">
+        <v>10</v>
+      </c>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
@@ -16902,17 +17117,27 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="F42" s="42">
+        <v>430</v>
+      </c>
+      <c r="G42" s="42">
+        <v>4</v>
+      </c>
       <c r="H42" s="42"/>
       <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>11</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
       <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
+      <c r="P42" s="42">
+        <v>10</v>
+      </c>
       <c r="Q42" s="43"/>
       <c r="R42" s="84" t="s">
         <v>54</v>
@@ -16955,7 +17180,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>13+54+10+368</f>
+        <v>445</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -16993,7 +17221,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -17363,11 +17592,19 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14">
+        <v>3</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>22</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -17383,8 +17620,12 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -17551,11 +17792,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>103</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -17571,19 +17820,31 @@
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>3</v>
+      </c>
+      <c r="F16" s="27">
+        <v>3</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>102</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -17599,8 +17860,12 @@
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="X16" s="62">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -17999,20 +18264,40 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14">
+        <v>1</v>
+      </c>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>6</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
+      <c r="H24" s="14">
+        <v>110</v>
+      </c>
+      <c r="I24" s="14">
+        <v>1</v>
+      </c>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>20</v>
+      </c>
+      <c r="M24" s="14">
+        <v>543</v>
+      </c>
+      <c r="N24" s="14">
+        <v>3</v>
+      </c>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -18185,20 +18470,40 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23"/>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
+      <c r="D31" s="23">
+        <v>0</v>
+      </c>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
+      <c r="H31" s="23">
+        <v>52</v>
+      </c>
+      <c r="I31" s="23">
+        <v>0</v>
+      </c>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>10</v>
+      </c>
+      <c r="M31" s="23">
+        <v>212</v>
+      </c>
+      <c r="N31" s="23">
+        <v>0</v>
+      </c>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -18213,20 +18518,40 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
+      <c r="C32" s="26">
+        <v>1</v>
+      </c>
+      <c r="D32" s="27">
+        <v>1</v>
+      </c>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>6</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="H32" s="28">
+        <v>58</v>
+      </c>
+      <c r="I32" s="28">
+        <v>1</v>
+      </c>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>10</v>
+      </c>
+      <c r="M32" s="28">
+        <v>331</v>
+      </c>
+      <c r="N32" s="28">
+        <v>3</v>
+      </c>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -18363,21 +18688,33 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>3</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>408</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>17</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>5</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>4</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>8</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -18521,21 +18858,33 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>3</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>408</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>17</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>5</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>4</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>8</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -18577,7 +18926,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>3+3+11+2+1+1+6+58+1+10+331+3</f>
+        <v>430</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -18585,7 +18937,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
+      <c r="C45" s="92">
+        <f>15</f>
+        <v>15</v>
+      </c>
       <c r="D45" s="92"/>
       <c r="E45" s="92"/>
     </row>
